--- a/Treinamento/Fiel_parte2.xlsx
+++ b/Treinamento/Fiel_parte2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65502581-BDC2-4330-8A80-208F6C41D00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B9951F-4802-431F-A513-8538561316B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,10 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -584,22 +584,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>129001878</v>
+        <v>129485896</v>
       </c>
       <c r="E2">
         <v>601</v>
       </c>
       <c r="F2" s="2">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="G2" s="2">
-        <v>45559</v>
+        <v>45560</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -622,22 +622,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>129458835</v>
+        <v>129511329</v>
       </c>
       <c r="E3">
         <v>601</v>
       </c>
       <c r="F3" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G3" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -660,16 +660,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>129461145</v>
+        <v>129513751</v>
       </c>
       <c r="E4">
         <v>601</v>
       </c>
       <c r="F4" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G4" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -698,16 +698,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>129462108</v>
+        <v>129518387</v>
       </c>
       <c r="E5">
         <v>601</v>
       </c>
       <c r="F5" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G5" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -736,22 +736,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>129463109</v>
+        <v>129521396</v>
       </c>
       <c r="E6">
         <v>601</v>
       </c>
       <c r="F6" s="2">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="G6" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -774,16 +774,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>129463306</v>
+        <v>129522217</v>
       </c>
       <c r="E7">
         <v>601</v>
       </c>
       <c r="F7" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G7" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -812,16 +812,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>129463712</v>
+        <v>129522877</v>
       </c>
       <c r="E8">
         <v>601</v>
       </c>
       <c r="F8" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G8" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -850,22 +850,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>129463867</v>
+        <v>129523466</v>
       </c>
       <c r="E9">
         <v>601</v>
       </c>
       <c r="F9" s="2">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="G9" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8003</v>
+        <v>8004</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -888,22 +888,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>129464558</v>
+        <v>129523480</v>
       </c>
       <c r="E10">
         <v>601</v>
       </c>
       <c r="F10" s="2">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="G10" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8003</v>
+        <v>8004</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -926,22 +926,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>129464587</v>
+        <v>129523646</v>
       </c>
       <c r="E11">
         <v>601</v>
       </c>
       <c r="F11" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G11" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -964,16 +964,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>129465175</v>
+        <v>129524108</v>
       </c>
       <c r="E12">
         <v>601</v>
       </c>
       <c r="F12" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G12" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1002,22 +1002,22 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>129465807</v>
+        <v>129524470</v>
       </c>
       <c r="E13">
         <v>601</v>
       </c>
       <c r="F13" s="2">
-        <v>45559</v>
+        <v>45563</v>
       </c>
       <c r="G13" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>1118</v>
+        <v>8013</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1040,16 +1040,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>129465874</v>
+        <v>129525110</v>
       </c>
       <c r="E14">
         <v>601</v>
       </c>
       <c r="F14" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G14" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1078,22 +1078,22 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>129466129</v>
+        <v>129525179</v>
       </c>
       <c r="E15">
         <v>601</v>
       </c>
       <c r="F15" s="2">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="G15" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1116,16 +1116,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>129466689</v>
+        <v>129525301</v>
       </c>
       <c r="E16">
         <v>601</v>
       </c>
       <c r="F16" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G16" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1154,22 +1154,22 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>129466809</v>
+        <v>129526957</v>
       </c>
       <c r="E17">
         <v>601</v>
       </c>
       <c r="F17" s="2">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="G17" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I17">
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1192,16 +1192,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>129466947</v>
+        <v>129527272</v>
       </c>
       <c r="E18">
         <v>601</v>
       </c>
       <c r="F18" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G18" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1230,22 +1230,22 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>129467452</v>
+        <v>129527378</v>
       </c>
       <c r="E19">
         <v>601</v>
       </c>
       <c r="F19" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G19" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I19">
         <v>42</v>
       </c>
       <c r="J19">
-        <v>1118</v>
+        <v>8004</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1268,22 +1268,22 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>129467677</v>
+        <v>129528001</v>
       </c>
       <c r="E20">
         <v>601</v>
       </c>
       <c r="F20" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G20" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1306,22 +1306,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>129469498</v>
+        <v>129528004</v>
       </c>
       <c r="E21">
         <v>601</v>
       </c>
       <c r="F21" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G21" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1344,22 +1344,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>129470271</v>
+        <v>129528014</v>
       </c>
       <c r="E22">
         <v>601</v>
       </c>
       <c r="F22" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G22" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1382,16 +1382,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>129470463</v>
+        <v>129528396</v>
       </c>
       <c r="E23">
         <v>601</v>
       </c>
       <c r="F23" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G23" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1420,22 +1420,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>129470660</v>
+        <v>129528879</v>
       </c>
       <c r="E24">
         <v>601</v>
       </c>
       <c r="F24" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G24" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1458,16 +1458,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>129471367</v>
+        <v>129529389</v>
       </c>
       <c r="E25">
         <v>601</v>
       </c>
       <c r="F25" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G25" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1496,16 +1496,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>129471471</v>
+        <v>129529448</v>
       </c>
       <c r="E26">
         <v>601</v>
       </c>
       <c r="F26" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G26" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1534,16 +1534,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>129471653</v>
+        <v>129529829</v>
       </c>
       <c r="E27">
         <v>601</v>
       </c>
       <c r="F27" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G27" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1572,22 +1572,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>129472049</v>
+        <v>129529860</v>
       </c>
       <c r="E28">
         <v>601</v>
       </c>
       <c r="F28" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G28" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1610,16 +1610,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>129473125</v>
+        <v>129530580</v>
       </c>
       <c r="E29">
         <v>601</v>
       </c>
       <c r="F29" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G29" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1648,22 +1648,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>129473451</v>
+        <v>129530829</v>
       </c>
       <c r="E30">
         <v>601</v>
       </c>
       <c r="F30" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G30" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1686,16 +1686,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>129473979</v>
+        <v>129531335</v>
       </c>
       <c r="E31">
         <v>601</v>
       </c>
       <c r="F31" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G31" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1724,22 +1724,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>129474133</v>
+        <v>129531619</v>
       </c>
       <c r="E32">
         <v>601</v>
       </c>
       <c r="F32" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G32" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1762,22 +1762,22 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>129474151</v>
+        <v>129531644</v>
       </c>
       <c r="E33">
         <v>601</v>
       </c>
       <c r="F33" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G33" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1800,22 +1800,22 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>129474769</v>
+        <v>129531645</v>
       </c>
       <c r="E34">
         <v>601</v>
       </c>
       <c r="F34" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G34" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1838,22 +1838,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>129474885</v>
+        <v>129532144</v>
       </c>
       <c r="E35">
         <v>601</v>
       </c>
       <c r="F35" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G35" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1876,22 +1876,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>129475068</v>
+        <v>129532269</v>
       </c>
       <c r="E36">
         <v>601</v>
       </c>
       <c r="F36" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G36" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1914,22 +1914,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>129475201</v>
+        <v>129532637</v>
       </c>
       <c r="E37">
         <v>601</v>
       </c>
       <c r="F37" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G37" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1952,16 +1952,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>129475205</v>
+        <v>129533593</v>
       </c>
       <c r="E38">
         <v>601</v>
       </c>
       <c r="F38" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G38" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>129475209</v>
+        <v>129533711</v>
       </c>
       <c r="E39">
         <v>601</v>
       </c>
       <c r="F39" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G39" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2028,22 +2028,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>129475211</v>
+        <v>129533851</v>
       </c>
       <c r="E40">
         <v>601</v>
       </c>
       <c r="F40" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="G40" s="2">
-        <v>45559</v>
+        <v>45562</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>129477815</v>
+        <v>129534792</v>
       </c>
       <c r="E41">
         <v>601</v>
       </c>
       <c r="F41" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G41" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2104,16 +2104,16 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>129478116</v>
+        <v>129535638</v>
       </c>
       <c r="E42">
         <v>601</v>
       </c>
       <c r="F42" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G42" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I42">
         <v>42</v>
@@ -2142,16 +2142,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>129478488</v>
+        <v>129535696</v>
       </c>
       <c r="E43">
         <v>601</v>
       </c>
       <c r="F43" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G43" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2180,22 +2180,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>129479035</v>
+        <v>129535996</v>
       </c>
       <c r="E44">
         <v>601</v>
       </c>
       <c r="F44" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G44" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>1118</v>
+        <v>8004</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2218,22 +2218,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>129479356</v>
+        <v>129536426</v>
       </c>
       <c r="E45">
         <v>601</v>
       </c>
       <c r="F45" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G45" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>1118</v>
+        <v>8004</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2256,16 +2256,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>129480522</v>
+        <v>129537282</v>
       </c>
       <c r="E46">
         <v>601</v>
       </c>
       <c r="F46" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="G46" s="2">
-        <v>45560</v>
+        <v>45562</v>
       </c>
       <c r="I46">
         <v>42</v>
@@ -2294,16 +2294,16 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>129480533</v>
+        <v>129539566</v>
       </c>
       <c r="E47">
         <v>601</v>
       </c>
       <c r="F47" s="2">
-        <v>45560</v>
+        <v>45563</v>
       </c>
       <c r="G47" s="2">
-        <v>45560</v>
+        <v>45563</v>
       </c>
       <c r="I47">
         <v>42</v>
@@ -2332,16 +2332,16 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>129481538</v>
+        <v>129539568</v>
       </c>
       <c r="E48">
         <v>601</v>
       </c>
       <c r="F48" s="2">
-        <v>45560</v>
+        <v>45563</v>
       </c>
       <c r="G48" s="2">
-        <v>45560</v>
+        <v>45563</v>
       </c>
       <c r="I48">
         <v>42</v>
@@ -2368,2975 +2368,323 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>129481790</v>
-      </c>
-      <c r="E49">
-        <v>601</v>
-      </c>
-      <c r="F49" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>8004</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>129482145</v>
-      </c>
-      <c r="E50">
-        <v>601</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>1118</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>129482286</v>
-      </c>
-      <c r="E51">
-        <v>601</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I51">
-        <v>42</v>
-      </c>
-      <c r="J51">
-        <v>1118</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>129482554</v>
-      </c>
-      <c r="E52">
-        <v>601</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I52">
-        <v>42</v>
-      </c>
-      <c r="J52">
-        <v>8004</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>129485887</v>
-      </c>
-      <c r="E53">
-        <v>601</v>
-      </c>
-      <c r="F53" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I53">
-        <v>42</v>
-      </c>
-      <c r="J53">
-        <v>8013</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>129485890</v>
-      </c>
-      <c r="E54">
-        <v>601</v>
-      </c>
-      <c r="F54" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I54">
-        <v>42</v>
-      </c>
-      <c r="J54">
-        <v>8013</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>129485896</v>
-      </c>
-      <c r="E55">
-        <v>601</v>
-      </c>
-      <c r="F55" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I55">
-        <v>42</v>
-      </c>
-      <c r="J55">
-        <v>8003</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>129485899</v>
-      </c>
-      <c r="E56">
-        <v>601</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I56">
-        <v>42</v>
-      </c>
-      <c r="J56">
-        <v>8003</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>129485931</v>
-      </c>
-      <c r="E57">
-        <v>601</v>
-      </c>
-      <c r="F57" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I57">
-        <v>42</v>
-      </c>
-      <c r="J57">
-        <v>8013</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>129486910</v>
-      </c>
-      <c r="E58">
-        <v>601</v>
-      </c>
-      <c r="F58" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I58">
-        <v>42</v>
-      </c>
-      <c r="J58">
-        <v>8004</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>129487626</v>
-      </c>
-      <c r="E59">
-        <v>601</v>
-      </c>
-      <c r="F59" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I59">
-        <v>42</v>
-      </c>
-      <c r="J59">
-        <v>8004</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>129488132</v>
-      </c>
-      <c r="E60">
-        <v>601</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>8004</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>129488518</v>
-      </c>
-      <c r="E61">
-        <v>601</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>8001</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>129488521</v>
-      </c>
-      <c r="E62">
-        <v>601</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>8004</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>129488710</v>
-      </c>
-      <c r="E63">
-        <v>601</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>8004</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>129489071</v>
-      </c>
-      <c r="E64">
-        <v>601</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>8004</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>129489102</v>
-      </c>
-      <c r="E65">
-        <v>601</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>8004</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>129489876</v>
-      </c>
-      <c r="E66">
-        <v>601</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>8004</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>129490108</v>
-      </c>
-      <c r="E67">
-        <v>601</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>8004</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>129491326</v>
-      </c>
-      <c r="E68">
-        <v>601</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>8004</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>129492447</v>
-      </c>
-      <c r="E69">
-        <v>601</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>8004</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>129493179</v>
-      </c>
-      <c r="E70">
-        <v>601</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>8004</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>129493262</v>
-      </c>
-      <c r="E71">
-        <v>601</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>8001</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>129493543</v>
-      </c>
-      <c r="E72">
-        <v>601</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>8004</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>129493840</v>
-      </c>
-      <c r="E73">
-        <v>601</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>8004</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>129497471</v>
-      </c>
-      <c r="E74">
-        <v>601</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>8004</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>129497679</v>
-      </c>
-      <c r="E75">
-        <v>601</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>8004</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>129499526</v>
-      </c>
-      <c r="E76">
-        <v>601</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>8001</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>129500381</v>
-      </c>
-      <c r="E77">
-        <v>601</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>8004</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>129502222</v>
-      </c>
-      <c r="E78">
-        <v>601</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>8004</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>129502890</v>
-      </c>
-      <c r="E79">
-        <v>601</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>8004</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>129503002</v>
-      </c>
-      <c r="E80">
-        <v>601</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>8004</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>129503549</v>
-      </c>
-      <c r="E81">
-        <v>601</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>8004</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>129506264</v>
-      </c>
-      <c r="E82">
-        <v>601</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>8013</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>129506266</v>
-      </c>
-      <c r="E83">
-        <v>601</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>8013</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>129506271</v>
-      </c>
-      <c r="E84">
-        <v>601</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>8013</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>129506273</v>
-      </c>
-      <c r="E85">
-        <v>601</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>8003</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>129506274</v>
-      </c>
-      <c r="E86">
-        <v>601</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>8013</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>129506278</v>
-      </c>
-      <c r="E87">
-        <v>601</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>8003</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>129506283</v>
-      </c>
-      <c r="E88">
-        <v>601</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>8013</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>129506288</v>
-      </c>
-      <c r="E89">
-        <v>601</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>8013</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>129506518</v>
-      </c>
-      <c r="E90">
-        <v>601</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>8004</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>129506556</v>
-      </c>
-      <c r="E91">
-        <v>601</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>8004</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>129506664</v>
-      </c>
-      <c r="E92">
-        <v>601</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>8004</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>129506948</v>
-      </c>
-      <c r="E93">
-        <v>601</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>8004</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>129507077</v>
-      </c>
-      <c r="E94">
-        <v>601</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I94">
-        <v>42</v>
-      </c>
-      <c r="J94">
-        <v>8004</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>129507751</v>
-      </c>
-      <c r="E95">
-        <v>601</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>8013</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>129509049</v>
-      </c>
-      <c r="E96">
-        <v>601</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I96">
-        <v>42</v>
-      </c>
-      <c r="J96">
-        <v>8004</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>129509138</v>
-      </c>
-      <c r="E97">
-        <v>601</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I97">
-        <v>42</v>
-      </c>
-      <c r="J97">
-        <v>8004</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>129510329</v>
-      </c>
-      <c r="E98">
-        <v>601</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I98">
-        <v>42</v>
-      </c>
-      <c r="J98">
-        <v>8013</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>129510335</v>
-      </c>
-      <c r="E99">
-        <v>601</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I99">
-        <v>42</v>
-      </c>
-      <c r="J99">
-        <v>8013</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>129510499</v>
-      </c>
-      <c r="E100">
-        <v>601</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I100">
-        <v>42</v>
-      </c>
-      <c r="J100">
-        <v>8004</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>129511579</v>
-      </c>
-      <c r="E101">
-        <v>601</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I101">
-        <v>42</v>
-      </c>
-      <c r="J101">
-        <v>8004</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>129511962</v>
-      </c>
-      <c r="E102">
-        <v>601</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
-        <v>8001</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>129512411</v>
-      </c>
-      <c r="E103">
-        <v>601</v>
-      </c>
-      <c r="F103" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G103" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>8004</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>129512740</v>
-      </c>
-      <c r="E104">
-        <v>601</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>8004</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>129512761</v>
-      </c>
-      <c r="E105">
-        <v>601</v>
-      </c>
-      <c r="F105" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G105" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-      <c r="J105">
-        <v>8004</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>129512862</v>
-      </c>
-      <c r="E106">
-        <v>601</v>
-      </c>
-      <c r="F106" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G106" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I106">
-        <v>42</v>
-      </c>
-      <c r="J106">
-        <v>8004</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>129513478</v>
-      </c>
-      <c r="E107">
-        <v>601</v>
-      </c>
-      <c r="F107" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G107" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I107">
-        <v>42</v>
-      </c>
-      <c r="J107">
-        <v>8004</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>129513494</v>
-      </c>
-      <c r="E108">
-        <v>601</v>
-      </c>
-      <c r="F108" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G108" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I108">
-        <v>42</v>
-      </c>
-      <c r="J108">
-        <v>8004</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>129513662</v>
-      </c>
-      <c r="E109">
-        <v>601</v>
-      </c>
-      <c r="F109" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G109" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I109">
-        <v>42</v>
-      </c>
-      <c r="J109">
-        <v>8004</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>129514737</v>
-      </c>
-      <c r="E110">
-        <v>601</v>
-      </c>
-      <c r="F110" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G110" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I110">
-        <v>42</v>
-      </c>
-      <c r="J110">
-        <v>8004</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>129514953</v>
-      </c>
-      <c r="E111">
-        <v>601</v>
-      </c>
-      <c r="F111" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G111" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8013</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>129514957</v>
-      </c>
-      <c r="E112">
-        <v>601</v>
-      </c>
-      <c r="F112" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G112" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I112">
-        <v>42</v>
-      </c>
-      <c r="J112">
-        <v>8013</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>129514962</v>
-      </c>
-      <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G113" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I113">
-        <v>42</v>
-      </c>
-      <c r="J113">
-        <v>8013</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>129514966</v>
-      </c>
-      <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G114" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I114">
-        <v>42</v>
-      </c>
-      <c r="J114">
-        <v>8013</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>129514968</v>
-      </c>
-      <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G115" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I115">
-        <v>42</v>
-      </c>
-      <c r="J115">
-        <v>8013</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>129514969</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G116" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8013</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>129515517</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G117" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8013</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>129515604</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G118" s="2">
-        <v>45561</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8013</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>129158340</v>
-      </c>
-      <c r="E119">
-        <v>601</v>
-      </c>
-      <c r="F119" s="2">
-        <v>45537</v>
-      </c>
-      <c r="G119" s="2">
-        <v>45537</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>129253487</v>
-      </c>
-      <c r="E120">
-        <v>601</v>
-      </c>
-      <c r="F120" s="2">
-        <v>45544</v>
-      </c>
-      <c r="G120" s="2">
-        <v>45544</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>129287173</v>
-      </c>
-      <c r="E121">
-        <v>601</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45547</v>
-      </c>
-      <c r="G121" s="2">
-        <v>45547</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>8004</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>129463023</v>
-      </c>
-      <c r="E122">
-        <v>601</v>
-      </c>
-      <c r="F122" s="2">
-        <v>45561</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45559</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>8013</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>129485513</v>
-      </c>
-      <c r="E123">
-        <v>601</v>
-      </c>
-      <c r="F123" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>129489096</v>
-      </c>
-      <c r="E124">
-        <v>601</v>
-      </c>
-      <c r="F124" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>129490219</v>
-      </c>
-      <c r="E125">
-        <v>601</v>
-      </c>
-      <c r="F125" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>8004</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>129494554</v>
-      </c>
-      <c r="E126">
-        <v>601</v>
-      </c>
-      <c r="F126" s="2">
-        <v>45560</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45560</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>1118</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+    </row>
+    <row r="75" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+    </row>
+    <row r="76" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+    </row>
+    <row r="77" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+    </row>
+    <row r="78" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+    </row>
+    <row r="79" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+    </row>
+    <row r="80" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+    </row>
+    <row r="93" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="96" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+    </row>
+    <row r="97" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+    </row>
+    <row r="98" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+    </row>
+    <row r="122" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+    </row>
+    <row r="123" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
     </row>
@@ -5457,6 +2805,7 @@
       <c r="G157" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q126" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -13046,31 +10395,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>